--- a/public/HAC_Junior_EA_PB_Certificates_2026.xlsx
+++ b/public/HAC_Junior_EA_PB_Certificates_2026.xlsx
@@ -552,7 +552,7 @@
   <dimension ref="A1:M112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="107" customWidth="1" min="1" max="1"/>
+    <col width="117" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Official England Athletics PB Award Certificates Summary (Track &amp; Field Season: 01.04.2026 - 30.09.2026)</t>
+          <t>Official England Athletics PB Award Certificates (Verified Standards March 2026 | Season: 01.04.2026 - 30.09.2026)</t>
         </is>
       </c>
     </row>
@@ -730,22 +730,22 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>1500m (4:16.24)</t>
+          <t>800m (1:56.48)</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>1500m: Level 9 | 200m: Level 4 | 3000m: Level 5 | 800m: Level 9 | Mile: Level 9</t>
+          <t>1500m: Level 5 | 200m: Level 4 | 3000m: Level 5 | 800m: Level 9 | Mile: Level 5</t>
         </is>
       </c>
       <c r="H6" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K6" s="9" t="n">
         <v>0</v>
@@ -845,14 +845,14 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>1500m: Level 9 | 400m: Level 6 | Mile: Level 9</t>
+          <t>1500m: Level 9 | 400m: Level 6 | Mile: Level 7</t>
         </is>
       </c>
       <c r="H8" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>1</v>
@@ -872,21 +872,21 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Elsie Fitzgerald</t>
+          <t>Henry Scott</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
@@ -895,22 +895,22 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>1500m (5:12.30)</t>
+          <t>200m (22.08)</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>1500m: Level 9 | 800m: Level 5</t>
+          <t>100m: Level 8 | 200m: Level 9 | High_Jump: Level 5 | Long_Jump: Level 5 | Triple_Jump: Level 4</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9" s="5" t="n">
         <v>0</v>
@@ -927,21 +927,21 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Emma Magerdichian</t>
+          <t>Hussein Issa</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
@@ -950,12 +950,12 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>1500m (5:03.0)</t>
+          <t>High_Jump (1.80)</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>1500m: Level 9 | 400m: Level 6 | 800m: Level 6</t>
+          <t>100m: Level 4 | 200m: Level 4 | High_Jump: Level 9 | Long_Jump: Level 6</t>
         </is>
       </c>
       <c r="H10" s="9" t="n">
@@ -965,7 +965,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
@@ -982,21 +982,21 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Henry Scott</t>
+          <t>Jana Issa</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>200m (22.08)</t>
+          <t>100m (13.14)</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 8 | 200m: Level 9 | High_Jump: Level 5 | Long_Jump: Level 5 | Triple_Jump: Level 4</t>
+          <t>100m: Level 9 | 200m: Level 9 | 60m: Level 7 | Long_Jump: Level 7</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" s="5" t="n">
         <v>0</v>
@@ -1037,7 +1037,7 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Hussein Issa</t>
+          <t>Sydney Taylor</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -1047,11 +1047,11 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>High_Jump (1.80)</t>
+          <t>100m (12.24)</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 4 | 200m: Level 4 | High_Jump: Level 9 | Long_Jump: Level 6</t>
+          <t>100m: Level 9 | 200m: Level 9</t>
         </is>
       </c>
       <c r="H12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
@@ -1092,7 +1092,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Jana Issa</t>
+          <t>Janaiah Mensah</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1106,31 +1106,31 @@
         </is>
       </c>
       <c r="D13" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Level 9</t>
+        <v>3</v>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Level 8</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>100m (13.14)</t>
+          <t>200m (28.20)</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 9 | 200m: Level 9 | 60m: Level 7 | Long_Jump: Level 7</t>
+          <t>100m: Level 6 | 200m: Level 8 | Long_Jump: Level 6</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="K13" s="5" t="n">
         <v>0</v>
@@ -1147,12 +1147,12 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Joshua Hounsell</t>
+          <t>Marcus Sery</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -1163,29 +1163,29 @@
       <c r="D14" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Level 9</t>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Level 8</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>1500m (4:38.51)</t>
+          <t>200m (25.04)</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>1500m: Level 9 | 800m: Level 4</t>
+          <t>100m: Level 7 | 200m: Level 8</t>
         </is>
       </c>
       <c r="H14" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>0</v>
@@ -1202,39 +1202,39 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Luke Sery</t>
+          <t>Stefania Onica</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Level 9</t>
+        <v>2</v>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Level 8</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>1500m (4:16.89)</t>
+          <t>200m (28.05)</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>1500m: Level 9 | 400m: Level 6 | 800m: Level 7</t>
+          <t>100m: Level 6 | 200m: Level 8</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="5" t="n">
         <v>1</v>
@@ -1257,42 +1257,42 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Sydney Taylor</t>
+          <t>Anton Yudichev</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Level 9</t>
+        <v>1</v>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Level 7</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>100m (12.24)</t>
+          <t>Javelin (48.64)</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 9 | 200m: Level 9</t>
+          <t>Javelin: Level 7</t>
         </is>
       </c>
       <c r="H16" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="9" t="n">
         <v>0</v>
@@ -1312,35 +1312,35 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Alexander Farley</t>
+          <t>Darcy Rae De Vere</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Level 8</t>
+          <t>Level 7</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>1500m (4:43.6)</t>
+          <t>200m (28.86)</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>1500m: Level 8</t>
+          <t>100m: Level 6 | 200m: Level 7 | High_Jump: Level 3 | Long_Jump: Level 4</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1350,10 +1350,10 @@
         <v>1</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="5" t="n">
         <v>0</v>
@@ -1367,35 +1367,35 @@
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Gia Patel</t>
+          <t>Elijah Williams</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Level 8</t>
+          <t>Level 7</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>1500m (5:40.54)</t>
+          <t>100m (12.69)</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>1500m: Level 8 | 800m: Club PB | High_Jump: Club PB</t>
+          <t>100m: Level 7 | 200m: Level 5</t>
         </is>
       </c>
       <c r="H18" s="9" t="n">
@@ -1405,13 +1405,13 @@
         <v>1</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Janaiah Mensah</t>
+          <t>Harry Prosser</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -1440,17 +1440,17 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>Level 8</t>
+          <t>Level 7</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>200m (28.20)</t>
+          <t>100m (12.6)</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 6 | 200m: Level 8 | Long_Jump: Level 6</t>
+          <t>100m: Level 7 | 200m: Level 6 | High_Jump: Level 5</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1477,7 +1477,7 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Marcus Sery</t>
+          <t>Hattie Stewart-Quantrell</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
@@ -1495,27 +1495,27 @@
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Level 8</t>
+          <t>Level 7</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>200m (25.04)</t>
+          <t>1500m (5:08.09)</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 7 | 200m: Level 8</t>
+          <t>1500m: Level 7 | 800m: Level 4</t>
         </is>
       </c>
       <c r="H20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Stefania Onica</t>
+          <t>Jacques Kriel</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1542,25 +1542,25 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="11" t="inlineStr">
         <is>
-          <t>Level 8</t>
+          <t>Level 7</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>200m (28.05)</t>
+          <t>Long_Jump (4.88)</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 6 | 200m: Level 8</t>
+          <t>100m: Level 5 | 200m: Level 4 | Long_Jump: Level 7</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1570,7 +1570,7 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" s="5" t="n">
         <v>0</v>
@@ -1587,35 +1587,35 @@
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Tabitha Kitching</t>
+          <t>Luke Sery</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Level 8</t>
+          <t>Level 7</t>
         </is>
       </c>
       <c r="F22" s="10" t="inlineStr">
         <is>
-          <t>1500m (5:38.81)</t>
+          <t>800m (1:59.94)</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>1500m: Level 8 | 800m: Level 1</t>
+          <t>1500m: Level 5 | 400m: Level 6 | 800m: Level 7</t>
         </is>
       </c>
       <c r="H22" s="9" t="n">
@@ -1625,10 +1625,10 @@
         <v>1</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
         <v>0</v>
@@ -1642,12 +1642,12 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Anton Yudichev</t>
+          <t>Nathan John Lewis</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
@@ -1665,12 +1665,12 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Javelin (48.64)</t>
+          <t>100m (11.78)</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Javelin: Level 7</t>
+          <t>100m: Level 7 | 200m: Level 6 | 800m: Club PB</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1680,13 +1680,13 @@
         <v>1</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
@@ -1697,21 +1697,21 @@
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Ava O'Sullivan</t>
+          <t>Reuben D'Souza</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
       </c>
       <c r="F24" s="10" t="inlineStr">
         <is>
-          <t>1500m (5:44.12)</t>
+          <t>400m (52.13)</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>1500m: Level 7 | 800m: Level 1</t>
+          <t>100m: Level 4 | 200m: Level 5 | 400m: Level 7</t>
         </is>
       </c>
       <c r="H24" s="9" t="n">
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
         <v>0</v>
@@ -1752,45 +1752,45 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Barnabe Lesenne-Ward</t>
+          <t>Anna Fear</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>Level 7</t>
+        <v>2</v>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Level 6</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>1500m (4:33.62)</t>
+          <t>1500m (5:14.98)</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>1500m: Level 7</t>
+          <t>1500m: Level 6 | 800m: Level 5</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" s="5" t="n">
         <v>0</v>
@@ -1807,48 +1807,48 @@
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Darcy Rae De Vere</t>
+          <t>Aryan Ramchurn</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>Level 7</t>
+        <v>2</v>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Level 6</t>
         </is>
       </c>
       <c r="F26" s="10" t="inlineStr">
         <is>
-          <t>200m (28.86)</t>
+          <t>100m (12.00)</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 6 | 200m: Level 7 | High_Jump: Level 3 | Long_Jump: Level 4</t>
+          <t>100m: Level 6 | Long_Jump: Level 4</t>
         </is>
       </c>
       <c r="H26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" s="9" t="n">
         <v>2</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
         <v>0</v>
@@ -1862,42 +1862,42 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Elijah Williams</t>
+          <t>Ava Wright</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>Level 7</t>
+        <v>1</v>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Level 6</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>100m (12.69)</t>
+          <t>400m (63.03)</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 7 | 200m: Level 5</t>
+          <t>400m: Level 6</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" s="5" t="n">
         <v>1</v>
@@ -1917,12 +1917,12 @@
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Harry Prosser</t>
+          <t>Cameron Morris</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -1931,28 +1931,28 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" s="11" t="inlineStr">
-        <is>
-          <t>Level 7</t>
+        <v>2</v>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>Level 6</t>
         </is>
       </c>
       <c r="F28" s="10" t="inlineStr">
         <is>
-          <t>100m (12.6)</t>
+          <t>100m (11.87)</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 7 | 200m: Level 6 | High_Jump: Level 5</t>
+          <t>100m: Level 6 | 200m: Level 6</t>
         </is>
       </c>
       <c r="H28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" s="9" t="n">
         <v>2</v>
@@ -1972,12 +1972,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Hattie Stewart-Quantrell</t>
+          <t>Dejonique Wilson</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -1986,28 +1986,28 @@
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" s="11" t="inlineStr">
-        <is>
-          <t>Level 7</t>
+        <v>1</v>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Level 6</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>1500m (5:08.09)</t>
+          <t>100m (13.08)</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>1500m: Level 7 | 800m: Level 4</t>
+          <t>100m: Level 6</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J29" s="5" t="n">
         <v>1</v>
@@ -2027,45 +2027,45 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Jacques Kriel</t>
+          <t>Emma Magerdichian</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="11" t="inlineStr">
-        <is>
-          <t>Level 7</t>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>Level 6</t>
         </is>
       </c>
       <c r="F30" s="10" t="inlineStr">
         <is>
-          <t>Long_Jump (4.88)</t>
+          <t>400m (63.73)</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 5 | 200m: Level 4 | Long_Jump: Level 7</t>
+          <t>1500m: Level 5 | 400m: Level 6 | 800m: Level 6</t>
         </is>
       </c>
       <c r="H30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0</v>
@@ -2082,12 +2082,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Nathan John Lewis</t>
+          <t>Jayden Mwatsama</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -2096,28 +2096,28 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" s="11" t="inlineStr">
-        <is>
-          <t>Level 7</t>
+        <v>1</v>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Level 6</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>100m (11.78)</t>
+          <t>High_Jump (1.45)</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 7 | 200m: Level 6 | 800m: Club PB</t>
+          <t>High_Jump: Level 6</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="5" t="n">
         <v>1</v>
@@ -2126,7 +2126,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
@@ -2137,42 +2137,42 @@
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Reuben D'Souza</t>
+          <t>Jessica Pope</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>Level 7</t>
+        <v>2</v>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>Level 6</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
         <is>
-          <t>400m (52.13)</t>
+          <t>200m (28.08)</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 4 | 200m: Level 5 | 400m: Level 7</t>
+          <t>100m: Level 4 | 200m: Level 6</t>
         </is>
       </c>
       <c r="H32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="9" t="n">
         <v>2</v>
@@ -2192,17 +2192,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Anna Fear</t>
+          <t>Khalid Amir</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>1500m (5:14.98)</t>
+          <t>100m (12.1)</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>1500m: Level 6 | 800m: Level 5</t>
+          <t>100m: Level 6 | 200m: Level 5</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2247,17 +2247,17 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Aryan Ramchurn</t>
+          <t>Lucy Adnett</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="F34" s="10" t="inlineStr">
         <is>
-          <t>100m (12.00)</t>
+          <t>High_Jump (1.35)</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 6 | Long_Jump: Level 4</t>
+          <t>High_Jump: Level 6 | Long_Jump: Level 5</t>
         </is>
       </c>
       <c r="H34" s="9" t="n">
@@ -2302,7 +2302,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Ava Wright</t>
+          <t>Nina Bakermans</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>400m (63.03)</t>
+          <t>200m (27.14)</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>400m: Level 6</t>
+          <t>100m: Club PB | 200m: Level 6</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2346,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Cameron Morris</t>
+          <t>Oliver Thompson</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
@@ -2380,12 +2380,12 @@
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>100m (11.87)</t>
+          <t>200m (24.09)</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 6 | 200m: Level 6</t>
+          <t>200m: Level 6 | Long_Jump: Level 4 | Triple_Jump: Level 6</t>
         </is>
       </c>
       <c r="H36" s="9" t="n">
@@ -2395,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0</v>
@@ -2412,7 +2412,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Dejonique Wilson</t>
+          <t>Tilly Hughes</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>100m (13.08)</t>
+          <t>200m (28.05)</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 6</t>
+          <t>100m: Level 4 | 200m: Level 6</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K37" s="5" t="n">
         <v>0</v>
@@ -2467,35 +2467,35 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Jayden Mwatsama</t>
+          <t>Alice Scott</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Level 6</t>
+          <t>Level 5</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>High_Jump (1.45)</t>
+          <t>High_Jump (1.44)</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>High_Jump: Level 6</t>
+          <t>High_Jump: Level 5 | Long_Jump: Level 3</t>
         </is>
       </c>
       <c r="H38" s="9" t="n">
@@ -2508,7 +2508,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="9" t="n">
         <v>0</v>
@@ -2522,12 +2522,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Jessica Pope</t>
+          <t>Anna Knight</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2540,17 +2540,17 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Level 6</t>
+          <t>Level 5</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>200m (28.08)</t>
+          <t>1500m (5:25.41)</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 4 | 200m: Level 6</t>
+          <t>1500m: Level 5 | 800m: Level 3</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2560,10 +2560,10 @@
         <v>0</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="5" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Khalid Amir</t>
+          <t>Annaliese Mosca</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
@@ -2595,17 +2595,17 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Level 6</t>
+          <t>Level 5</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>100m (12.1)</t>
+          <t>200m (28.75)</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 6 | 200m: Level 5</t>
+          <t>100m: Level 3 | 200m: Level 5</t>
         </is>
       </c>
       <c r="H40" s="9" t="n">
@@ -2615,10 +2615,10 @@
         <v>0</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="9" t="n">
         <v>0</v>
@@ -2632,7 +2632,7 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Lucy Adnett</t>
+          <t>Chloe McBride</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Level 6</t>
+          <t>Level 5</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>High_Jump (1.35)</t>
+          <t>100m (14.1)</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>High_Jump: Level 6 | Long_Jump: Level 5</t>
+          <t>100m: Level 5 | 200m: Level 5</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2687,12 +2687,12 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>Masha Karunaratne</t>
+          <t>Dara Bassey</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -2701,21 +2701,21 @@
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Level 6</t>
+          <t>Level 5</t>
         </is>
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>1500m (5:56.05)</t>
+          <t>Long_Jump (4.07)</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>1500m: Level 6</t>
+          <t>100m: Level 3 | Long_Jump: Level 5</t>
         </is>
       </c>
       <c r="H42" s="9" t="n">
@@ -2728,7 +2728,7 @@
         <v>1</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="9" t="n">
         <v>0</v>
@@ -2742,17 +2742,17 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Nina Bakermans</t>
+          <t>David Utete</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Level 6</t>
+          <t>Level 5</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>200m (27.14)</t>
+          <t>100m (12.15)</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>100m: Club PB | 200m: Level 6</t>
+          <t>100m: Level 5 | 200m: Level 5</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2780,13 +2780,13 @@
         <v>0</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>Oliver Thompson</t>
+          <t>Elsie Fitzgerald</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -2807,25 +2807,25 @@
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Level 6</t>
+          <t>Level 5</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>200m (24.09)</t>
+          <t>800m (2:26.18)</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>200m: Level 6 | Long_Jump: Level 4 | Triple_Jump: Level 6</t>
+          <t>1500m: Level 4 | 800m: Level 5</t>
         </is>
       </c>
       <c r="H44" s="9" t="n">
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>0</v>
@@ -2852,7 +2852,7 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Tilly Hughes</t>
+          <t>Jack Kerr</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -2862,25 +2862,25 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Level 6</t>
+          <t>Level 5</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>200m (28.05)</t>
+          <t>800m (2:09.96)</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 4 | 200m: Level 6</t>
+          <t>800m: Level 5</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2890,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K45" s="5" t="n">
         <v>0</v>
@@ -2907,21 +2907,21 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>Alice Scott</t>
+          <t>Kacey Mccalmon</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="F46" s="10" t="inlineStr">
         <is>
-          <t>High_Jump (1.44)</t>
+          <t>200m (26.51)</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>High_Jump: Level 5 | Long_Jump: Level 3</t>
+          <t>100m: Level 1 | 200m: Level 5 | 800m: Club PB</t>
         </is>
       </c>
       <c r="H46" s="9" t="n">
@@ -2951,7 +2951,7 @@
         <v>1</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" s="9" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Anna Knight</t>
+          <t>Leo Barton</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>1500m (5:25.41)</t>
+          <t>100m (13.17)</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>1500m: Level 5 | 800m: Level 3</t>
+          <t>100m: Level 5 | 200m: Level 3</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3017,7 +3017,7 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>Annaliese Mosca</t>
+          <t>Rayen Webster</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>200m (28.75)</t>
+          <t>200m (28.6)</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 3 | 200m: Level 5</t>
+          <t>100m: Level 2 | 200m: Level 5</t>
         </is>
       </c>
       <c r="H48" s="9" t="n">
@@ -3072,12 +3072,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Chloe McBride</t>
+          <t>Shauna Mensah</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -3086,34 +3086,34 @@
         </is>
       </c>
       <c r="D49" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" s="12" t="inlineStr">
+        <is>
+          <t>Level 5</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>200m (27.4)</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>100m: Level 3 | 200m: Level 5 | Long_Jump: Level 2</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>Level 5</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>100m (14.1)</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>100m: Level 5 | 200m: Level 5</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K49" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="L49" s="5" t="n">
         <v>0</v>
@@ -3127,21 +3127,21 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>Dara Bassey</t>
+          <t>William Glynn</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
@@ -3150,12 +3150,12 @@
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>Long_Jump (4.07)</t>
+          <t>200m (23.6)</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 3 | Long_Jump: Level 5</t>
+          <t>100m: Level 4 | 200m: Level 5 | Long_Jump: Level 5 | Triple_Jump: Level 4</t>
         </is>
       </c>
       <c r="H50" s="9" t="n">
@@ -3165,10 +3165,10 @@
         <v>0</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
         <v>0</v>
@@ -3182,17 +3182,17 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>David Utete</t>
+          <t>Aleah Salehi-Reyhani</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Level 5</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>100m (12.15)</t>
+          <t>800m (2:38.19)</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 5 | 200m: Level 5</t>
+          <t>1500m: Level 3 | 800m: Level 4</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3220,10 +3220,10 @@
         <v>0</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="5" t="n">
         <v>0</v>
@@ -3237,12 +3237,12 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>Jack Kerr</t>
+          <t>Alessio Neroni</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U20</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
@@ -3255,17 +3255,17 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Level 5</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>800m (2:09.96)</t>
+          <t>Long_Jump (5.92)</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>800m: Level 5</t>
+          <t>Long_Jump: Level 4</t>
         </is>
       </c>
       <c r="H52" s="9" t="n">
@@ -3292,12 +3292,12 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Kacey Mccalmon</t>
+          <t>Alexander Farley</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -3306,21 +3306,21 @@
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Level 5</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>200m (26.51)</t>
+          <t>1500m (4:43.6)</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 1 | 200m: Level 5 | 800m: Club PB</t>
+          <t>1500m: Level 4</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3333,10 +3333,10 @@
         <v>1</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
@@ -3347,12 +3347,12 @@
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>Leo Barton</t>
+          <t>Alexander Shotton</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>Level 5</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>100m (13.17)</t>
+          <t>Discus (27.53)</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 5 | 200m: Level 3</t>
+          <t>Discus: Level 4 | Javelin: Club PB | Shot: Club PB</t>
         </is>
       </c>
       <c r="H54" s="9" t="n">
@@ -3388,10 +3388,10 @@
         <v>1</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M54" s="9" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Rayen Webster</t>
+          <t>Amariah Odogwu</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -3420,17 +3420,17 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Level 5</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>200m (28.6)</t>
+          <t>200m (29.6)</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 2 | 200m: Level 5</t>
+          <t>200m: Level 4 | 800m: Club PB</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3443,10 +3443,10 @@
         <v>1</v>
       </c>
       <c r="K55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="L55" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
@@ -3457,12 +3457,12 @@
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>Shauna Mensah</t>
+          <t>Amelia Elizabeth Angel...</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
@@ -3471,21 +3471,21 @@
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Level 5</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="F56" s="10" t="inlineStr">
         <is>
-          <t>200m (27.4)</t>
+          <t>200m (29.80)</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 3 | 200m: Level 5 | Long_Jump: Level 2</t>
+          <t>200m: Level 4</t>
         </is>
       </c>
       <c r="H56" s="9" t="n">
@@ -3498,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
         <v>0</v>
@@ -3512,7 +3512,7 @@
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>William Glynn</t>
+          <t>Archie Wall</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -3530,17 +3530,17 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Level 5</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>200m (23.6)</t>
+          <t>Discus (28.16)</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 4 | 200m: Level 5 | Long_Jump: Level 5 | Triple_Jump: Level 4</t>
+          <t>100m: Club PB | Discus: Level 4 | Hammer: Club PB | Shot: Level 1</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3550,13 +3550,13 @@
         <v>0</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
@@ -3567,21 +3567,21 @@
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>Aleah Salehi-Reyhani</t>
+          <t>Diego Monteiro</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="F58" s="10" t="inlineStr">
         <is>
-          <t>800m (2:38.19)</t>
+          <t>100m (12.36)</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>1500m: Level 3 | 800m: Level 4</t>
+          <t>100m: Level 4</t>
         </is>
       </c>
       <c r="H58" s="9" t="n">
@@ -3608,7 +3608,7 @@
         <v>1</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="9" t="n">
         <v>0</v>
@@ -3622,12 +3622,12 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Alessio Neroni</t>
+          <t>Ethan Denith Peiris</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>U20</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Long_Jump (5.92)</t>
+          <t>Long_Jump (4.36)</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -3677,7 +3677,7 @@
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>Alexander Shotton</t>
+          <t>Evan Allen</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="F60" s="10" t="inlineStr">
         <is>
-          <t>Discus (27.53)</t>
+          <t>400m (56.3)</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>Discus: Level 4 | Javelin: Club PB | Shot: Club PB</t>
+          <t>400m: Level 4 | Long_Jump: Level 1</t>
         </is>
       </c>
       <c r="H60" s="9" t="n">
@@ -3718,10 +3718,10 @@
         <v>1</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M60" s="9" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Amariah Odogwu</t>
+          <t>Ganieve Juttla</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>200m (29.6)</t>
+          <t>High_Jump (1.35)</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>200m: Level 4 | 800m: Club PB</t>
+          <t>800m: Level 1 | High_Jump: Level 4</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3773,10 +3773,10 @@
         <v>1</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
@@ -3787,12 +3787,12 @@
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>Amelia Elizabeth Angel...</t>
+          <t>Itxaso Chamoto-Zubimendi</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>200m (29.80)</t>
+          <t>100m (12.92)</t>
         </is>
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>200m: Level 4</t>
+          <t>100m: Level 4</t>
         </is>
       </c>
       <c r="H62" s="9" t="n">
@@ -3842,12 +3842,12 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Archie Wall</t>
+          <t>Joshua Hounsell</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
@@ -3865,12 +3865,12 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Discus (28.16)</t>
+          <t>1500m (4:38.51)</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>100m: Club PB | Discus: Level 4 | Hammer: Club PB | Shot: Level 1</t>
+          <t>1500m: Level 4 | 800m: Level 4</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3880,13 +3880,13 @@
         <v>0</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
@@ -3897,12 +3897,12 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>Diego Monteiro</t>
+          <t>Lewis Wake</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
@@ -3911,37 +3911,37 @@
         </is>
       </c>
       <c r="D64" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t>Level 4</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>High_Jump (1.65)</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>1500m: Club PB | 400m: Level 2 | 800m: Level 2 | High_Jump: Level 4 | Long_Jump: Level 2 | Triple_Jump: Level 4</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L64" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="E64" s="12" t="inlineStr">
-        <is>
-          <t>Level 4</t>
-        </is>
-      </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t>100m (12.36)</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t>100m: Level 4</t>
-        </is>
-      </c>
-      <c r="H64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="M64" s="9" t="inlineStr">
         <is>
@@ -3952,21 +3952,21 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Ethan Denith Peiris</t>
+          <t>Rosa Chiapponi</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
@@ -3975,12 +3975,12 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Long_Jump (4.36)</t>
+          <t>200m (29.22)</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>Long_Jump: Level 4</t>
+          <t>200m: Level 4 | Long_Jump: Level 4</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3990,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K65" s="5" t="n">
         <v>0</v>
@@ -4007,7 +4007,7 @@
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>Evan Allen</t>
+          <t>Senuk Hiroon Ihalagedara</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="F66" s="10" t="inlineStr">
         <is>
-          <t>400m (56.3)</t>
+          <t>100m (11.9)</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>400m: Level 4 | Long_Jump: Level 1</t>
+          <t>100m: Level 4 | 200m: Level 3</t>
         </is>
       </c>
       <c r="H66" s="9" t="n">
@@ -4062,21 +4062,21 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Ganieve Juttla</t>
+          <t>Steffan Coates</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
@@ -4085,12 +4085,12 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>High_Jump (1.35)</t>
+          <t>Long_Jump (4.37)</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>800m: Level 1 | High_Jump: Level 4</t>
+          <t>200m: Level 1 | High_Jump: Level 1 | Long_Jump: Level 4</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4103,7 +4103,7 @@
         <v>1</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" s="5" t="n">
         <v>0</v>
@@ -4117,12 +4117,12 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>Itxaso Chamoto-Zubimendi</t>
+          <t>Wiktoria Kucharska</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="F68" s="10" t="inlineStr">
         <is>
-          <t>100m (12.92)</t>
+          <t>Long_Jump (3.75)</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 4</t>
+          <t>Long_Jump: Level 4</t>
         </is>
       </c>
       <c r="H68" s="9" t="n">
@@ -4172,12 +4172,12 @@
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Lewis Wake</t>
+          <t>Finlay Kybert</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -4186,21 +4186,21 @@
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E69" s="12" t="inlineStr">
-        <is>
-          <t>Level 4</t>
+        <v>2</v>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>High_Jump (1.65)</t>
+          <t>1500m (5:19.99)</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>1500m: Level 2 | 400m: Level 2 | 800m: Level 2 | High_Jump: Level 4 | Long_Jump: Level 2 | Triple_Jump: Level 4</t>
+          <t>1500m: Level 3 | 800m: Level 1</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4210,10 +4210,10 @@
         <v>0</v>
       </c>
       <c r="J69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="K69" s="5" t="n">
-        <v>4</v>
       </c>
       <c r="L69" s="5" t="n">
         <v>0</v>
@@ -4227,12 +4227,12 @@
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>Rosa Chiapponi</t>
+          <t>Grace Saha</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
@@ -4243,19 +4243,19 @@
       <c r="D70" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E70" s="12" t="inlineStr">
-        <is>
-          <t>Level 4</t>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
         <is>
-          <t>200m (29.22)</t>
+          <t>800m (2:44.74)</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>200m: Level 4 | Long_Jump: Level 4</t>
+          <t>1500m: Club PB | 800m: Level 3</t>
         </is>
       </c>
       <c r="H70" s="9" t="n">
@@ -4265,13 +4265,13 @@
         <v>0</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="9" t="inlineStr">
         <is>
@@ -4282,12 +4282,12 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Senuk Hiroon Ihalagedara</t>
+          <t>Isaac D'Souza</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -4296,21 +4296,21 @@
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E71" s="12" t="inlineStr">
-        <is>
-          <t>Level 4</t>
+        <v>3</v>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>100m (11.9)</t>
+          <t>800m (2:28.66)</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 4 | 200m: Level 3</t>
+          <t>100m: Level 1 | 200m: Level 2 | 800m: Level 3</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L71" s="5" t="n">
         <v>0</v>
@@ -4337,7 +4337,7 @@
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>Steffan Coates</t>
+          <t>Isabelle Robinson</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
@@ -4347,25 +4347,25 @@
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="E72" s="12" t="inlineStr">
-        <is>
-          <t>Level 4</t>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
         <is>
-          <t>Long_Jump (4.37)</t>
+          <t>100m (14.68)</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>200m: Level 1 | High_Jump: Level 1 | Long_Jump: Level 4</t>
+          <t>100m: Level 3 | 1500m: Club PB | 800m: Level 3</t>
         </is>
       </c>
       <c r="H72" s="9" t="n">
@@ -4375,13 +4375,13 @@
         <v>0</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="9" t="inlineStr">
         <is>
@@ -4392,12 +4392,12 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Wiktoria Kucharska</t>
+          <t>Kyra Byrne</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -4406,21 +4406,21 @@
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" s="12" t="inlineStr">
-        <is>
-          <t>Level 4</t>
+        <v>3</v>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Long_Jump (3.75)</t>
+          <t>Long_Jump (4.22)</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>Long_Jump: Level 4</t>
+          <t>100m: Level 1 | 200m: Level 2 | Long_Jump: Level 3</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -4430,10 +4430,10 @@
         <v>0</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L73" s="5" t="n">
         <v>0</v>
@@ -4447,7 +4447,7 @@
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>Alastair Burton</t>
+          <t>Levita Threadgold</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
@@ -4457,11 +4457,11 @@
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="F74" s="10" t="inlineStr">
         <is>
-          <t>1500m (5:15.00)</t>
+          <t>Discus (20.42)</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>1500m: Level 3 | 800m: Club PB</t>
+          <t>Discus: Level 3</t>
         </is>
       </c>
       <c r="H74" s="9" t="n">
@@ -4491,7 +4491,7 @@
         <v>1</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M74" s="9" t="inlineStr">
         <is>
@@ -4502,7 +4502,7 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Finlay Kybert</t>
+          <t>Lois Wagjiani</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
@@ -4512,11 +4512,11 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
@@ -4525,12 +4525,12 @@
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>1500m (5:19.99)</t>
+          <t>800m (2:41.35)</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>1500m: Level 3 | 800m: Level 1</t>
+          <t>800m: Level 3</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4543,7 +4543,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L75" s="5" t="n">
         <v>0</v>
@@ -4557,7 +4557,7 @@
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>Grace Saha</t>
+          <t>Samuel Watson</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
@@ -4567,41 +4567,41 @@
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>Level 3</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>Long_Jump (4.06)</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>100m: Club PB | 800m: Club PB | High_Jump: Level 1 | Long_Jump: Level 3</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>Level 3</t>
-        </is>
-      </c>
-      <c r="F76" s="10" t="inlineStr">
-        <is>
-          <t>800m (2:44.74)</t>
-        </is>
-      </c>
-      <c r="G76" s="10" t="inlineStr">
-        <is>
-          <t>1500m: Club PB | 800m: Level 3</t>
-        </is>
-      </c>
-      <c r="H76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="L76" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M76" s="9" t="inlineStr">
         <is>
@@ -4612,7 +4612,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Isaac D'Souza</t>
+          <t>Thomas Owen</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="D77" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
@@ -4635,12 +4635,12 @@
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>800m (2:28.66)</t>
+          <t>1500m (5:10.79)</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 1 | 200m: Level 2 | 800m: Level 3</t>
+          <t>1500m: Level 3</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4653,7 +4653,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L77" s="5" t="n">
         <v>0</v>
@@ -4667,35 +4667,35 @@
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>Isabelle Robinson</t>
+          <t>Barnabe Lesenne-Ward</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="F78" s="10" t="inlineStr">
         <is>
-          <t>100m (14.68)</t>
+          <t>1500m (4:33.62)</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 3 | 1500m: Club PB | 800m: Level 3</t>
+          <t>1500m: Level 2</t>
         </is>
       </c>
       <c r="H78" s="9" t="n">
@@ -4708,10 +4708,10 @@
         <v>0</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" s="9" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Kyra Byrne</t>
+          <t>Emma Uwatse</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
@@ -4736,21 +4736,21 @@
         </is>
       </c>
       <c r="D79" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Long_Jump (4.22)</t>
+          <t>100m (14.0)</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 1 | 200m: Level 2 | Long_Jump: Level 3</t>
+          <t>100m: Level 2</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4763,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L79" s="5" t="n">
         <v>0</v>
@@ -4777,35 +4777,35 @@
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>Levita Threadgold</t>
+          <t>Emmanuel Nnatuanya</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="F80" s="10" t="inlineStr">
         <is>
-          <t>Discus (20.42)</t>
+          <t>100m (14.3)</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>Discus: Level 3</t>
+          <t>100m: Level 2 | Long_Jump: Level 2</t>
         </is>
       </c>
       <c r="H80" s="9" t="n">
@@ -4818,7 +4818,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L80" s="9" t="n">
         <v>0</v>
@@ -4832,17 +4832,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Lois Wagjiani</t>
+          <t>Ethan Dong O'Connor</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D81" s="5" t="n">
@@ -4850,17 +4850,17 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>800m (2:41.35)</t>
+          <t>200m (26.12)</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>800m: Level 3</t>
+          <t>200m: Level 2</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4887,35 +4887,35 @@
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>Samuel Watson</t>
+          <t>Hollie Ford</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U20</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="F82" s="10" t="inlineStr">
         <is>
-          <t>Long_Jump (4.06)</t>
+          <t>400m (68.81)</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>100m: Club PB | 800m: Club PB | High_Jump: Level 1 | Long_Jump: Level 3</t>
+          <t>400m: Level 2</t>
         </is>
       </c>
       <c r="H82" s="9" t="n">
@@ -4928,10 +4928,10 @@
         <v>0</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M82" s="9" t="inlineStr">
         <is>
@@ -4942,12 +4942,12 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Thomas Owen</t>
+          <t>Joseph Holmes</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="D83" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>1500m (5:10.79)</t>
+          <t>400m (60.2)</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>1500m: Level 3</t>
+          <t>400m: Level 2 | 800m: Club PB</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4986,7 +4986,7 @@
         <v>1</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
@@ -4997,21 +4997,21 @@
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>Edey Kestell</t>
+          <t>Mason Hamdy</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
@@ -5020,12 +5020,12 @@
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>1500m (5:59.96)</t>
+          <t>800m (2:18.98)</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>1500m: Level 2 | 800m: Club PB</t>
+          <t>800m: Level 2</t>
         </is>
       </c>
       <c r="H84" s="9" t="n">
@@ -5041,7 +5041,7 @@
         <v>1</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M84" s="9" t="inlineStr">
         <is>
@@ -5052,17 +5052,17 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Emma Uwatse</t>
+          <t>Murad Alexander Alzahr</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D85" s="5" t="n">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>100m (14.0)</t>
+          <t>100m (14.45)</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
@@ -5107,7 +5107,7 @@
     <row r="86">
       <c r="A86" s="8" t="inlineStr">
         <is>
-          <t>Emmanuel Nnatuanya</t>
+          <t>Niamh Cuddihy</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
@@ -5117,11 +5117,11 @@
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
@@ -5130,12 +5130,12 @@
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>100m (14.3)</t>
+          <t>1500m (5:48.30)</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>100m: Level 2 | Long_Jump: Level 2</t>
+          <t>1500m: Level 2</t>
         </is>
       </c>
       <c r="H86" s="9" t="n">
@@ -5148,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L86" s="9" t="n">
         <v>0</v>
@@ -5162,12 +5162,12 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Ethan Dong O'Connor</t>
+          <t>Noah Jones</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="D87" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
@@ -5185,12 +5185,12 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>200m (26.12)</t>
+          <t>1500m (5:21.74)</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>200m: Level 2</t>
+          <t>1500m: Level 2 | 800m: Level 1</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" s="5" t="n">
         <v>0</v>
@@ -5217,12 +5217,12 @@
     <row r="88">
       <c r="A88" s="8" t="inlineStr">
         <is>
-          <t>Hollie Ford</t>
+          <t>Rhea Abbi</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>U20</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
@@ -5240,12 +5240,12 @@
       </c>
       <c r="F88" s="10" t="inlineStr">
         <is>
-          <t>400m (68.81)</t>
+          <t>200m (31.10)</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>400m: Level 2</t>
+          <t>100m: Club PB | 200m: Level 2</t>
         </is>
       </c>
       <c r="H88" s="9" t="n">
@@ -5261,7 +5261,7 @@
         <v>1</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="9" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Joseph Holmes</t>
+          <t>Shauna Ohemeng Mensah</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D89" s="5" t="n">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>400m (60.2)</t>
+          <t>100m (13.42)</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>400m: Level 2 | 800m: Club PB</t>
+          <t>100m: Level 2 | Long_Jump: Club PB</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -5327,21 +5327,21 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>Mason Hamdy</t>
+          <t>Zoe Morse</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
@@ -5350,12 +5350,12 @@
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>800m (2:18.98)</t>
+          <t>Discus (22.23)</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>800m: Level 2</t>
+          <t>Discus: Level 2 | Javelin: Level 1</t>
         </is>
       </c>
       <c r="H90" s="9" t="n">
@@ -5368,7 +5368,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L90" s="9" t="n">
         <v>0</v>
@@ -5382,12 +5382,12 @@
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Murad Alexander Alzahr</t>
+          <t>Aiden Sutherland</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -5400,17 +5400,17 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>100m (14.45)</t>
+          <t>100m (13.43)</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 2</t>
+          <t>100m: Level 1</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -5437,35 +5437,35 @@
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>Niamh Cuddihy</t>
+          <t>Alastair Burton</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="F92" s="10" t="inlineStr">
         <is>
-          <t>1500m (5:48.30)</t>
+          <t>1500m (5:15.00)</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>1500m: Level 2</t>
+          <t>1500m: Level 1 | 800m: Club PB</t>
         </is>
       </c>
       <c r="H92" s="9" t="n">
@@ -5481,7 +5481,7 @@
         <v>1</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="9" t="inlineStr">
         <is>
@@ -5492,35 +5492,35 @@
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Noah Jones</t>
+          <t>Anastasia Muiznieks</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D93" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>1500m (5:21.74)</t>
+          <t>Discus (16.24)</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>1500m: Level 2 | 800m: Level 1</t>
+          <t>Discus: Level 1</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -5533,7 +5533,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L93" s="5" t="n">
         <v>0</v>
@@ -5547,7 +5547,7 @@
     <row r="94">
       <c r="A94" s="8" t="inlineStr">
         <is>
-          <t>Rhea Abbi</t>
+          <t>Ava O'Sullivan</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
@@ -5565,17 +5565,17 @@
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
         <is>
-          <t>200m (31.10)</t>
+          <t>1500m (5:44.12)</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>100m: Club PB | 200m: Level 2</t>
+          <t>1500m: Level 1 | 800m: Level 1</t>
         </is>
       </c>
       <c r="H94" s="9" t="n">
@@ -5588,10 +5588,10 @@
         <v>0</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="9" t="inlineStr">
         <is>
@@ -5602,17 +5602,17 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Shauna Ohemeng Mensah</t>
+          <t>Freddie Wright</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D95" s="5" t="n">
@@ -5620,17 +5620,17 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>100m (13.42)</t>
+          <t>200m (26.8)</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 2 | Long_Jump: Club PB</t>
+          <t>200m: Level 1 | 800m: Club PB</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -5657,12 +5657,12 @@
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>Zoe Morse</t>
+          <t>Gia Patel</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
@@ -5671,37 +5671,37 @@
         </is>
       </c>
       <c r="D96" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>1500m (5:40.54)</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>1500m: Level 1 | 800m: Club PB | High_Jump: Club PB</t>
+        </is>
+      </c>
+      <c r="H96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="E96" s="8" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="F96" s="10" t="inlineStr">
-        <is>
-          <t>Discus (22.23)</t>
-        </is>
-      </c>
-      <c r="G96" s="10" t="inlineStr">
-        <is>
-          <t>Discus: Level 2 | Javelin: Level 1</t>
-        </is>
-      </c>
-      <c r="H96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L96" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="M96" s="9" t="inlineStr">
         <is>
@@ -5712,12 +5712,12 @@
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Aiden Sutherland</t>
+          <t>Lewis Mayhew</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -5735,12 +5735,12 @@
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>100m (13.43)</t>
+          <t>1500m (5:37.40)</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 1</t>
+          <t>1500m: Level 1</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5767,7 +5767,7 @@
     <row r="98">
       <c r="A98" s="8" t="inlineStr">
         <is>
-          <t>Anastasia Muiznieks</t>
+          <t>Lola Webb</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="F98" s="10" t="inlineStr">
         <is>
-          <t>Discus (16.24)</t>
+          <t>100m (14.07)</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>Discus: Level 1</t>
+          <t>100m: Level 1</t>
         </is>
       </c>
       <c r="H98" s="9" t="n">
@@ -5822,17 +5822,17 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Freddie Wright</t>
+          <t>Rebekah Francis-Rennie</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D99" s="5" t="n">
@@ -5845,12 +5845,12 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>200m (26.8)</t>
+          <t>800m (2:50.67)</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>200m: Level 1 | 800m: Club PB</t>
+          <t>1500m: Club PB | 800m: Level 1</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -5877,21 +5877,21 @@
     <row r="100">
       <c r="A100" s="8" t="inlineStr">
         <is>
-          <t>Lewis Mayhew</t>
+          <t>Tabitha Kitching</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
@@ -5900,12 +5900,12 @@
       </c>
       <c r="F100" s="10" t="inlineStr">
         <is>
-          <t>1500m (5:37.40)</t>
+          <t>1500m (5:38.81)</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>1500m: Level 1</t>
+          <t>1500m: Level 1 | 800m: Level 1</t>
         </is>
       </c>
       <c r="H100" s="9" t="n">
@@ -5918,7 +5918,7 @@
         <v>0</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L100" s="9" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Lola Webb</t>
+          <t>Yana Gudka</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>100m (14.07)</t>
+          <t>Triple_Jump (8.82)</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>100m: Level 1</t>
+          <t>Triple_Jump: Level 1</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5987,12 +5987,12 @@
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>Rebekah Francis-Rennie</t>
+          <t>Ada Florence Mitchell</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
@@ -6001,21 +6001,21 @@
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Club PB Award</t>
         </is>
       </c>
       <c r="F102" s="10" t="inlineStr">
         <is>
-          <t>800m (2:50.67)</t>
+          <t>800m (2:49.88)</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>1500m: Club PB | 800m: Level 1</t>
+          <t>800m: Club PB</t>
         </is>
       </c>
       <c r="H102" s="9" t="n">
@@ -6028,7 +6028,7 @@
         <v>0</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="9" t="n">
         <v>1</v>
@@ -6042,7 +6042,7 @@
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Yana Gudka</t>
+          <t>Adam Strinic</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
@@ -6052,25 +6052,25 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D103" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Level 1</t>
+          <t>Club PB Award</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Triple_Jump (8.82)</t>
+          <t>3000m (13:14.0)</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>Triple_Jump: Level 1</t>
+          <t>3000m: Club PB | 800m: Club PB</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>Ada Florence Mitchell</t>
+          <t>Cara Traynor</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>800m (2:49.88)</t>
+          <t>800m (2:51.29)</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
@@ -6152,21 +6152,21 @@
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Adam Strinic</t>
+          <t>Charna-Jo Booth</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D105" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
@@ -6175,12 +6175,12 @@
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>3000m (13:14.0)</t>
+          <t>800m (3:03.52)</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>3000m: Club PB | 800m: Club PB</t>
+          <t>800m: Club PB</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -6196,7 +6196,7 @@
         <v>0</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M105" s="5" t="inlineStr">
         <is>
@@ -6207,12 +6207,12 @@
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>Cara Traynor</t>
+          <t>Edey Kestell</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
@@ -6221,7 +6221,7 @@
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
@@ -6230,12 +6230,12 @@
       </c>
       <c r="F106" s="10" t="inlineStr">
         <is>
-          <t>800m (2:51.29)</t>
+          <t>1500m (5:59.96)</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>800m: Club PB</t>
+          <t>1500m: Club PB | 800m: Club PB</t>
         </is>
       </c>
       <c r="H106" s="9" t="n">
@@ -6251,7 +6251,7 @@
         <v>0</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M106" s="9" t="inlineStr">
         <is>
@@ -6262,12 +6262,12 @@
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Charna-Jo Booth</t>
+          <t>Elissa Deuter</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U18</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
@@ -6276,7 +6276,7 @@
         </is>
       </c>
       <c r="D107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
@@ -6285,12 +6285,12 @@
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>800m (3:03.52)</t>
+          <t>400m (79.28)</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>800m: Club PB</t>
+          <t>400m: Club PB | 800m: Club PB</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M107" s="5" t="inlineStr">
         <is>
@@ -6317,21 +6317,21 @@
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>Elissa Deuter</t>
+          <t>Jacob Gredelj</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>U18</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Girls/Women</t>
+          <t>Boys/Men</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
@@ -6340,12 +6340,12 @@
       </c>
       <c r="F108" s="10" t="inlineStr">
         <is>
-          <t>400m (79.28)</t>
+          <t>1500m (6:00.87)</t>
         </is>
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>400m: Club PB | 800m: Club PB</t>
+          <t>1500m: Club PB</t>
         </is>
       </c>
       <c r="H108" s="9" t="n">
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M108" s="9" t="inlineStr">
         <is>
@@ -6372,17 +6372,17 @@
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Jacob Gredelj</t>
+          <t>Masha Karunaratne</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Boys/Men</t>
+          <t>Girls/Women</t>
         </is>
       </c>
       <c r="D109" s="5" t="n">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>1500m (6:00.87)</t>
+          <t>1500m (5:56.05)</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
@@ -6591,8 +6591,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11376,22 +11376,22 @@
       </c>
       <c r="F80" s="19" t="inlineStr">
         <is>
-          <t>Level 3</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>EA Level 3 Award</t>
+          <t>EA Level 1 Award</t>
         </is>
       </c>
       <c r="H80" s="16" t="inlineStr">
         <is>
-          <t>5:16.00</t>
+          <t>5:15.00</t>
         </is>
       </c>
       <c r="I80" s="16" t="inlineStr">
         <is>
-          <t>5:10.00</t>
+          <t>5:05.00</t>
         </is>
       </c>
       <c r="J80" s="9" t="inlineStr">
@@ -11498,24 +11498,24 @@
           <t>4:43.6</t>
         </is>
       </c>
-      <c r="F82" s="15" t="inlineStr">
-        <is>
-          <t>Level 8</t>
+      <c r="F82" s="17" t="inlineStr">
+        <is>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>EA Level 8 Award</t>
+          <t>EA Level 4 Award</t>
         </is>
       </c>
       <c r="H82" s="16" t="inlineStr">
         <is>
-          <t>4:48.00</t>
+          <t>4:45.00</t>
         </is>
       </c>
       <c r="I82" s="16" t="inlineStr">
         <is>
-          <t>4:43.00</t>
+          <t>4:37.50</t>
         </is>
       </c>
       <c r="J82" s="9" t="inlineStr">
@@ -12676,24 +12676,24 @@
           <t>4:38.51</t>
         </is>
       </c>
-      <c r="F101" s="20" t="inlineStr">
-        <is>
-          <t>Level 9</t>
+      <c r="F101" s="17" t="inlineStr">
+        <is>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>EA Level 9 Award</t>
+          <t>EA Level 4 Award</t>
         </is>
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
-          <t>4:43.00</t>
+          <t>4:45.00</t>
         </is>
       </c>
       <c r="I101" s="14" t="inlineStr">
         <is>
-          <t>Max Level</t>
+          <t>4:37.50</t>
         </is>
       </c>
       <c r="J101" s="5" t="inlineStr">
@@ -13792,24 +13792,24 @@
           <t>5:44.12</t>
         </is>
       </c>
-      <c r="F119" s="15" t="inlineStr">
-        <is>
-          <t>Level 7</t>
+      <c r="F119" s="18" t="inlineStr">
+        <is>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>EA Level 7 Award</t>
+          <t>EA Level 1 Award</t>
         </is>
       </c>
       <c r="H119" s="14" t="inlineStr">
         <is>
-          <t>5:50.00</t>
+          <t>5:45.00</t>
         </is>
       </c>
       <c r="I119" s="14" t="inlineStr">
         <is>
-          <t>5:42.00</t>
+          <t>5:35.00</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
@@ -14102,24 +14102,24 @@
           <t>5:12.30</t>
         </is>
       </c>
-      <c r="F124" s="20" t="inlineStr">
-        <is>
-          <t>Level 9</t>
+      <c r="F124" s="17" t="inlineStr">
+        <is>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>EA Level 9 Award</t>
+          <t>EA Level 4 Award</t>
         </is>
       </c>
       <c r="H124" s="16" t="inlineStr">
         <is>
-          <t>5:36.00</t>
+          <t>5:16.00</t>
         </is>
       </c>
       <c r="I124" s="16" t="inlineStr">
         <is>
-          <t>Max Level</t>
+          <t>5:09.00</t>
         </is>
       </c>
       <c r="J124" s="9" t="inlineStr">
@@ -14412,24 +14412,24 @@
           <t>5:40.54</t>
         </is>
       </c>
-      <c r="F129" s="15" t="inlineStr">
-        <is>
-          <t>Level 8</t>
+      <c r="F129" s="18" t="inlineStr">
+        <is>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>EA Level 8 Award</t>
+          <t>EA Level 1 Award</t>
         </is>
       </c>
       <c r="H129" s="14" t="inlineStr">
         <is>
-          <t>5:42.00</t>
+          <t>5:45.00</t>
         </is>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>5:36.00</t>
+          <t>5:35.00</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
@@ -15032,24 +15032,24 @@
           <t>5:56.05</t>
         </is>
       </c>
-      <c r="F139" s="17" t="inlineStr">
-        <is>
-          <t>Level 6</t>
+      <c r="F139" s="18" t="inlineStr">
+        <is>
+          <t>Club PB</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>EA Level 6 Award</t>
+          <t>Club PB Recognition</t>
         </is>
       </c>
       <c r="H139" s="14" t="inlineStr">
         <is>
-          <t>5:58.00</t>
+          <t>Below Level 1</t>
         </is>
       </c>
       <c r="I139" s="14" t="inlineStr">
         <is>
-          <t>5:50.00</t>
+          <t>L1: 5:45.00</t>
         </is>
       </c>
       <c r="J139" s="5" t="inlineStr">
@@ -15714,24 +15714,24 @@
           <t>5:38.81</t>
         </is>
       </c>
-      <c r="F150" s="15" t="inlineStr">
-        <is>
-          <t>Level 8</t>
+      <c r="F150" s="19" t="inlineStr">
+        <is>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>EA Level 8 Award</t>
+          <t>EA Level 1 Award</t>
         </is>
       </c>
       <c r="H150" s="16" t="inlineStr">
         <is>
-          <t>5:42.00</t>
+          <t>5:45.00</t>
         </is>
       </c>
       <c r="I150" s="16" t="inlineStr">
         <is>
-          <t>5:36.00</t>
+          <t>5:35.00</t>
         </is>
       </c>
       <c r="J150" s="9" t="inlineStr">
@@ -16582,24 +16582,24 @@
           <t>4:33.62</t>
         </is>
       </c>
-      <c r="F164" s="15" t="inlineStr">
-        <is>
-          <t>Level 7</t>
+      <c r="F164" s="19" t="inlineStr">
+        <is>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>EA Level 7 Award</t>
+          <t>EA Level 2 Award</t>
         </is>
       </c>
       <c r="H164" s="16" t="inlineStr">
         <is>
-          <t>4:34.00</t>
+          <t>4:40.00</t>
         </is>
       </c>
       <c r="I164" s="16" t="inlineStr">
         <is>
-          <t>4:32.00</t>
+          <t>4:32.50</t>
         </is>
       </c>
       <c r="J164" s="9" t="inlineStr">
@@ -16644,24 +16644,24 @@
           <t>4:16.24</t>
         </is>
       </c>
-      <c r="F165" s="20" t="inlineStr">
-        <is>
-          <t>Level 9</t>
+      <c r="F165" s="17" t="inlineStr">
+        <is>
+          <t>Level 5</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
         <is>
-          <t>EA Level 9 Award</t>
+          <t>EA Level 5 Award</t>
         </is>
       </c>
       <c r="H165" s="14" t="inlineStr">
         <is>
-          <t>4:30.00</t>
+          <t>4:20.00</t>
         </is>
       </c>
       <c r="I165" s="14" t="inlineStr">
         <is>
-          <t>Max Level</t>
+          <t>4:15.00</t>
         </is>
       </c>
       <c r="J165" s="5" t="inlineStr">
@@ -16892,24 +16892,24 @@
           <t>4:38.57</t>
         </is>
       </c>
-      <c r="F169" s="20" t="inlineStr">
-        <is>
-          <t>Level 9</t>
+      <c r="F169" s="17" t="inlineStr">
+        <is>
+          <t>Level 5</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
-          <t>EA Level 9 Award</t>
+          <t>EA Level 5 Award</t>
         </is>
       </c>
       <c r="H169" s="14" t="inlineStr">
         <is>
-          <t>4:30.00</t>
+          <t>4:20.00</t>
         </is>
       </c>
       <c r="I169" s="14" t="inlineStr">
         <is>
-          <t>Max Level</t>
+          <t>4:15.00</t>
         </is>
       </c>
       <c r="J169" s="5" t="inlineStr">
@@ -16966,7 +16966,7 @@
       </c>
       <c r="H170" s="16" t="inlineStr">
         <is>
-          <t>4:30.00</t>
+          <t>4:01.25</t>
         </is>
       </c>
       <c r="I170" s="16" t="inlineStr">
@@ -17078,24 +17078,24 @@
           <t>4:25.27</t>
         </is>
       </c>
-      <c r="F172" s="20" t="inlineStr">
-        <is>
-          <t>Level 9</t>
+      <c r="F172" s="15" t="inlineStr">
+        <is>
+          <t>Level 7</t>
         </is>
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>EA Level 9 Award</t>
+          <t>EA Level 7 Award</t>
         </is>
       </c>
       <c r="H172" s="16" t="inlineStr">
         <is>
-          <t>4:30.00</t>
+          <t>4:10.00</t>
         </is>
       </c>
       <c r="I172" s="16" t="inlineStr">
         <is>
-          <t>Max Level</t>
+          <t>4:05.00</t>
         </is>
       </c>
       <c r="J172" s="9" t="inlineStr">
@@ -17700,22 +17700,22 @@
       </c>
       <c r="F182" s="19" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Club PB</t>
         </is>
       </c>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t>EA Level 2 Award</t>
+          <t>Club PB Recognition</t>
         </is>
       </c>
       <c r="H182" s="16" t="inlineStr">
         <is>
-          <t>4:58.00</t>
+          <t>Below Level 1</t>
         </is>
       </c>
       <c r="I182" s="16" t="inlineStr">
         <is>
-          <t>4:53.00</t>
+          <t>L1: 4:50.00</t>
         </is>
       </c>
       <c r="J182" s="9" t="inlineStr">
@@ -18070,24 +18070,24 @@
           <t>4:16.89</t>
         </is>
       </c>
-      <c r="F188" s="20" t="inlineStr">
-        <is>
-          <t>Level 9</t>
+      <c r="F188" s="17" t="inlineStr">
+        <is>
+          <t>Level 5</t>
         </is>
       </c>
       <c r="G188" s="8" t="inlineStr">
         <is>
-          <t>EA Level 9 Award</t>
+          <t>EA Level 5 Award</t>
         </is>
       </c>
       <c r="H188" s="16" t="inlineStr">
         <is>
-          <t>4:30.00</t>
+          <t>4:20.00</t>
         </is>
       </c>
       <c r="I188" s="16" t="inlineStr">
         <is>
-          <t>Max Level</t>
+          <t>4:15.00</t>
         </is>
       </c>
       <c r="J188" s="9" t="inlineStr">
@@ -19126,22 +19126,22 @@
       </c>
       <c r="F205" s="18" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Club PB</t>
         </is>
       </c>
       <c r="G205" s="4" t="inlineStr">
         <is>
-          <t>EA Level 2 Award</t>
+          <t>Club PB Recognition</t>
         </is>
       </c>
       <c r="H205" s="14" t="inlineStr">
         <is>
-          <t>6:08.00</t>
+          <t>Below Level 1</t>
         </is>
       </c>
       <c r="I205" s="14" t="inlineStr">
         <is>
-          <t>5:59.00</t>
+          <t>L1: 5:35.00</t>
         </is>
       </c>
       <c r="J205" s="5" t="inlineStr">
@@ -19372,24 +19372,24 @@
           <t>5:03.0</t>
         </is>
       </c>
-      <c r="F209" s="20" t="inlineStr">
-        <is>
-          <t>Level 9</t>
+      <c r="F209" s="17" t="inlineStr">
+        <is>
+          <t>Level 5</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
         <is>
-          <t>EA Level 9 Award</t>
+          <t>EA Level 5 Award</t>
         </is>
       </c>
       <c r="H209" s="14" t="inlineStr">
         <is>
-          <t>5:20.00</t>
+          <t>5:03.00</t>
         </is>
       </c>
       <c r="I209" s="14" t="inlineStr">
         <is>
-          <t>Max Level</t>
+          <t>4:57.50</t>
         </is>
       </c>
       <c r="J209" s="5" t="inlineStr">
@@ -20402,8 +20402,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
